--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -569,13 +569,7 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Is there a maximum allowable response time (in milliseconds) for the firmware to acknowledge a hardware interrupt?
-Should the system log or report missed or delayed interrupts for diagnostic purposes?
-Are there different priority levels for interrupts that require differentiated response handling?</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -644,13 +638,7 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>After three failed connection attempts, should the firmware continue retrying indefinitely or enter a defined error state?
-Is there a required backoff interval or algorithm between consecutive connection retries?
-Should the user be notified locally (e.g., via LED or display) when the connection cannot be established?</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -5966,13 +5966,7 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Is there a maximum response time (in milliseconds) that the firmware must meet when processing user input events?
-Should the firmware provide any user feedback (e.g., LED blink, sound) if the input event cannot be processed within the expected time?
-Are there specific user roles that require different latency thresholds for input event handling?</t>
-        </is>
-      </c>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -6040,13 +6034,7 @@
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Should the firmware distinguish between transient and persistent communication failures when reporting errors?
-Is there a requirement to log communication failure events for later diagnostics?
-Are there predefined error codes that must be used for communication failures, or should new codes be defined?</t>
-        </is>
-      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -9944,13 +9932,7 @@
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>Is there a maximum allowable latency (in milliseconds or seconds) between receiving the firmware update command and initiating the update process?
-Should the system provide a user-visible confirmation (e.g., LED indicator, log message) when the firmware update process starts?
-Are there any specific error states that must be reported if the firmware update initiation fails?</t>
-        </is>
-      </c>
+      <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
@@ -10018,13 +10000,7 @@
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>Are all user roles (e.g., admin, operator, guest) authorized to access the diagnostics interface?
-If access is restricted, should unauthorized access attempts be logged or trigger an alert?
-Is multi-factor authentication required for accessing the diagnostics interface?</t>
-        </is>
-      </c>
+      <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
@@ -12573,7 +12549,13 @@
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Is there a maximum allowable latency (in milliseconds) for processing and acknowledging user input events?
+Should the system queue or discard user input events received during ongoing processing?
+Are there specific error states or notifications required if input event processing exceeds the defined latency threshold?</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -12641,7 +12623,13 @@
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Is access to the advanced configuration panel restricted to administrator-level users only?
+Should failed access attempts to the advanced configuration panel be logged for audit purposes?
+Are there different permission levels within the advanced configuration panel, or is access binary (all-or-nothing)?</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -12709,7 +12697,13 @@
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Should the system retry communication automatically upon failure, or require manual intervention?
+Is there a maximum number of retry attempts before the system declares a permanent failure state?
+Must the user be notified immediately in the event of a communication failure, or is silent logging sufficient?</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -15293,7 +15287,13 @@
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Should the device attempt automatic reconnection if the initial network connection fails? (Yes/No)
+Is there a maximum number of reconnection attempts before the device reports a failure state?
+What specific error message or code should be logged or displayed to the user upon persistent network connection failure?</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
@@ -15361,7 +15361,13 @@
         </is>
       </c>
       <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Is there a maximum acceptable latency (in milliseconds) between user input and system response?
+Should the system prioritize certain user input events over others in cases of simultaneous inputs?
+Are there any user roles or contexts where input event processing latency requirements differ?</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
@@ -16650,13 +16656,7 @@
         </is>
       </c>
       <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>Is there a predefined list or classification for 'critical errors' that the firmware must detect? (Yes/No)
-Should the system halt all operations immediately upon detecting a critical error, or attempt a controlled shutdown?
-What is the expected latency between error detection and system response (in milliseconds)?</t>
-        </is>
-      </c>
+      <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -16720,13 +16720,7 @@
         </is>
       </c>
       <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>Is real-time synchronization (deterministic timing) required, or is eventual consistency acceptable?
-What is the maximum allowable delay (in milliseconds) for data propagation between modules?
-Should the system log synchronization failures, and if so, at what severity level?</t>
-        </is>
-      </c>
+      <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
     </row>
     <row r="244">

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -858,7 +858,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -2224,7 +2224,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -4811,7 +4811,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
     </row>
@@ -4879,7 +4883,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
     </row>
@@ -4947,7 +4955,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
     </row>
@@ -6107,7 +6119,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -6177,7 +6189,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
     </row>
@@ -6245,7 +6261,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
     </row>
@@ -6313,7 +6333,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
     </row>
@@ -7371,7 +7395,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
     </row>
@@ -7440,7 +7468,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
     </row>
@@ -7508,7 +7540,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
     </row>
@@ -7576,7 +7612,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
     </row>
@@ -7646,7 +7686,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
     </row>
@@ -8770,7 +8814,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O123" t="inlineStr"/>
@@ -8844,11 +8888,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
     </row>
@@ -8916,11 +8956,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
     </row>
@@ -8989,11 +9025,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
     </row>
@@ -12816,7 +12848,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
     </row>
@@ -12884,7 +12920,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
     </row>
@@ -12952,7 +12992,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
     </row>
@@ -14114,7 +14158,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O203" t="inlineStr"/>
@@ -14184,7 +14228,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
     </row>
@@ -14252,7 +14300,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
     </row>
@@ -14320,7 +14372,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
     </row>
@@ -15482,7 +15538,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O223" t="inlineStr"/>
@@ -15552,11 +15608,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
     </row>
@@ -15624,11 +15676,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
     </row>
@@ -15696,11 +15744,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
     </row>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -858,7 +858,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -929,11 +929,7 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -1002,11 +998,7 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -1075,11 +1067,7 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -2008,7 +2008,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2078,11 +2078,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
     </row>
@@ -2150,11 +2146,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
     </row>
@@ -2222,11 +2214,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
     </row>
@@ -3367,7 +3355,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
@@ -3436,11 +3424,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
     </row>
@@ -3505,11 +3489,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
     </row>
@@ -3577,11 +3557,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
     </row>
@@ -6107,7 +6083,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -6177,11 +6153,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
     </row>
@@ -6249,11 +6221,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
     </row>
@@ -6321,11 +6289,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
     </row>
@@ -11435,7 +11399,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O163" t="inlineStr"/>
@@ -11505,11 +11469,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
     </row>
@@ -11577,11 +11537,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
     </row>
@@ -11649,11 +11605,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
     </row>
@@ -12790,7 +12742,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O183" t="inlineStr"/>
@@ -12860,11 +12812,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
     </row>
@@ -12932,11 +12880,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
     </row>
@@ -13004,11 +12948,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
     </row>
@@ -14386,7 +14326,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O206" t="inlineStr"/>
@@ -15766,7 +15706,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O226" t="inlineStr"/>
@@ -16923,7 +16863,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O243" t="inlineStr"/>
@@ -16989,7 +16929,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
     </row>
@@ -17053,7 +16997,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
     </row>
@@ -17117,7 +17065,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
     </row>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -706,11 +706,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -778,11 +774,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -850,11 +842,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2008,7 +1996,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2078,7 +2066,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
     </row>
@@ -2146,7 +2138,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
     </row>
@@ -2214,7 +2210,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
@@ -3424,7 +3424,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
     </row>
@@ -3489,7 +3493,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
     </row>
@@ -3557,7 +3565,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
     </row>
@@ -4717,7 +4729,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -4787,7 +4799,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
     </row>
@@ -4855,7 +4871,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
     </row>
@@ -4923,7 +4943,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
     </row>
@@ -8766,7 +8790,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O123" t="inlineStr"/>
@@ -8840,11 +8864,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
     </row>
@@ -8912,11 +8932,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
     </row>
@@ -8985,11 +9001,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
     </row>
@@ -11399,7 +11411,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O163" t="inlineStr"/>
@@ -11469,7 +11481,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
     </row>
@@ -11537,7 +11553,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
     </row>
@@ -11605,7 +11625,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
     </row>
@@ -14110,7 +14134,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O203" t="inlineStr"/>
@@ -14180,11 +14204,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
     </row>
@@ -14252,11 +14272,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
     </row>
@@ -14324,11 +14340,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
     </row>
@@ -16863,7 +16875,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O243" t="inlineStr"/>
@@ -16929,11 +16941,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
     </row>
@@ -16997,11 +17005,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
     </row>
@@ -17065,11 +17069,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
     </row>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -706,7 +706,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -774,7 +778,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -842,7 +850,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2068,7 +2080,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -2140,7 +2152,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -2212,7 +2224,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -4945,7 +4957,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -7518,7 +7530,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
@@ -7590,7 +7602,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O105" t="inlineStr"/>
@@ -7664,7 +7676,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O106" t="inlineStr"/>
@@ -8790,7 +8802,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O123" t="inlineStr"/>
@@ -8864,7 +8876,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
     </row>
@@ -8932,7 +8948,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
     </row>
@@ -9001,7 +9021,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
     </row>
@@ -9070,7 +9094,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
     </row>
@@ -10109,7 +10137,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O143" t="inlineStr"/>
@@ -10179,11 +10207,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
     </row>
@@ -10251,11 +10275,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
     </row>
@@ -10323,11 +10343,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
     </row>
@@ -12766,7 +12782,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O183" t="inlineStr"/>
@@ -12836,7 +12852,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
     </row>
@@ -12904,7 +12924,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
     </row>
@@ -12972,7 +12996,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
     </row>
@@ -14134,7 +14162,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O203" t="inlineStr"/>
@@ -14204,7 +14232,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
     </row>
@@ -14272,7 +14304,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
     </row>
@@ -14340,7 +14376,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
     </row>
@@ -16875,7 +16915,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O243" t="inlineStr"/>
@@ -16941,7 +16981,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
     </row>
@@ -17005,7 +17049,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
     </row>
@@ -17069,7 +17117,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
     </row>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -716,7 +716,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -789,7 +789,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -573,7 +573,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>What is the maximum acceptable response time in milliseconds?
+Which component — frontend, backend, or network — owns this response time requirement?
+Under what load conditions (concurrent users, requests/second) must this be met?</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -643,7 +649,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -714,11 +720,7 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -787,11 +789,7 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -856,11 +854,7 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>

--- a/output_prd.xlsx
+++ b/output_prd.xlsx
@@ -575,9 +575,9 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>What is the maximum acceptable response time in milliseconds?
-Which component — frontend, backend, or network — owns this response time requirement?
-Under what load conditions (concurrent users, requests/second) must this be met?</t>
+          <t>What specific metric defines 'efficient'? For example, is it power consumption, processing speed, or resource utilization?
+What is the acceptable range or value for this metric (e.g., in watts, ms, or percentage)?
+Which system or actor is responsible for meeting this requirement?</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -649,10 +649,15 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>What unit should be applied to the threshold value (e.g., seconds, bytes, percentage)?
+Which specific system or actor is responsible for ensuring this threshold is met?</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -720,8 +725,18 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>What measurable criteria define 'robust'? For example, is it uptime percentage, fault tolerance, or error rate?
+What is the acceptable threshold for this criterion?
+Which component or actor is responsible for ensuring robustness?</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -789,7 +804,11 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -854,8 +873,18 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>What specific conditions trigger the requirement to be implemented?
+What is the measurable threshold for this requirement once triggered?
+Which system or actor is responsible for implementing this requirement?</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
